--- a/resources/templates/standard/J3100-05.xlsx
+++ b/resources/templates/standard/J3100-05.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="23">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>변경점 관리 계획 대비 실적</t>
   </si>
@@ -549,12 +552,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.5" customHeight="1" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -581,21 +586,21 @@
       <c r="AB1" s="2"/>
       <c r="AC1" s="2"/>
       <c r="AD1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE1" s="3"/>
       <c r="AF1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG1" s="4"/>
       <c r="AH1" s="4"/>
       <c r="AI1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ1" s="4"/>
       <c r="AK1" s="4"/>
       <c r="AL1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM1" s="4"/>
       <c r="AN1" s="4"/>
@@ -796,27 +801,27 @@
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
@@ -830,7 +835,7 @@
       <c r="W5" s="4"/>
       <c r="X5" s="4"/>
       <c r="Y5" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z5" s="4"/>
       <c r="AA5" s="4"/>
@@ -844,7 +849,7 @@
       <c r="AI5" s="4"/>
       <c r="AJ5" s="4"/>
       <c r="AK5" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL5" s="4"/>
       <c r="AM5" s="4"/>
@@ -893,27 +898,27 @@
       <c r="W6" s="4"/>
       <c r="X6" s="4"/>
       <c r="Y6" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z6" s="7"/>
       <c r="AA6" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB6" s="7"/>
       <c r="AC6" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD6" s="7"/>
       <c r="AE6" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF6" s="7"/>
       <c r="AG6" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH6" s="7"/>
       <c r="AI6" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ6" s="7"/>
       <c r="AK6" s="4"/>
@@ -1037,60 +1042,60 @@
       <c r="K8" s="9"/>
       <c r="L8" s="9"/>
       <c r="M8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N8" s="10"/>
       <c r="O8" s="10"/>
       <c r="P8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q8" s="10"/>
       <c r="R8" s="10"/>
       <c r="S8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T8" s="10"/>
       <c r="U8" s="10"/>
       <c r="V8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="W8" s="10"/>
       <c r="X8" s="10"/>
       <c r="Y8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AC8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AD8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK8" s="1"/>
       <c r="AL8" s="1"/>
@@ -1140,40 +1145,40 @@
       <c r="W9" s="10"/>
       <c r="X9" s="10"/>
       <c r="Y9" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA9" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB9" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC9" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD9" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE9" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF9" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG9" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH9" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI9" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ9" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK9" s="1"/>
       <c r="AL9" s="1"/>
@@ -1225,40 +1230,40 @@
       <c r="W10" s="10"/>
       <c r="X10" s="10"/>
       <c r="Y10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AC10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AD10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK10" s="1"/>
       <c r="AL10" s="1"/>
@@ -1308,40 +1313,40 @@
       <c r="W11" s="10"/>
       <c r="X11" s="10"/>
       <c r="Y11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB11" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD11" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF11" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH11" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ11" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK11" s="1"/>
       <c r="AL11" s="1"/>
@@ -1393,40 +1398,40 @@
       <c r="W12" s="10"/>
       <c r="X12" s="10"/>
       <c r="Y12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AC12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AD12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK12" s="1"/>
       <c r="AL12" s="1"/>
@@ -1476,40 +1481,40 @@
       <c r="W13" s="10"/>
       <c r="X13" s="10"/>
       <c r="Y13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK13" s="1"/>
       <c r="AL13" s="1"/>
@@ -1561,40 +1566,40 @@
       <c r="W14" s="10"/>
       <c r="X14" s="10"/>
       <c r="Y14" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA14" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AC14" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AD14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE14" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG14" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI14" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK14" s="1"/>
       <c r="AL14" s="1"/>
@@ -1644,40 +1649,40 @@
       <c r="W15" s="10"/>
       <c r="X15" s="10"/>
       <c r="Y15" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA15" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC15" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE15" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG15" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI15" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK15" s="1"/>
       <c r="AL15" s="1"/>
@@ -1729,40 +1734,40 @@
       <c r="W16" s="10"/>
       <c r="X16" s="10"/>
       <c r="Y16" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA16" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AC16" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AD16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE16" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG16" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI16" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK16" s="1"/>
       <c r="AL16" s="1"/>
@@ -1812,40 +1817,40 @@
       <c r="W17" s="10"/>
       <c r="X17" s="10"/>
       <c r="Y17" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z17" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA17" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB17" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC17" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD17" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE17" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF17" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG17" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH17" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI17" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ17" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK17" s="1"/>
       <c r="AL17" s="1"/>
@@ -1897,40 +1902,40 @@
       <c r="W18" s="10"/>
       <c r="X18" s="10"/>
       <c r="Y18" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z18" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA18" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB18" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AC18" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AD18" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE18" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF18" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG18" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH18" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI18" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ18" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK18" s="1"/>
       <c r="AL18" s="1"/>
@@ -1980,40 +1985,40 @@
       <c r="W19" s="10"/>
       <c r="X19" s="10"/>
       <c r="Y19" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z19" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA19" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB19" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC19" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD19" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE19" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF19" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG19" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH19" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI19" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ19" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK19" s="1"/>
       <c r="AL19" s="1"/>
@@ -2065,40 +2070,40 @@
       <c r="W20" s="10"/>
       <c r="X20" s="10"/>
       <c r="Y20" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z20" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA20" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB20" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AC20" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AD20" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE20" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF20" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG20" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH20" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI20" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ20" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK20" s="1"/>
       <c r="AL20" s="1"/>
@@ -2148,40 +2153,40 @@
       <c r="W21" s="10"/>
       <c r="X21" s="10"/>
       <c r="Y21" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z21" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA21" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB21" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC21" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD21" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE21" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF21" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG21" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH21" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI21" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ21" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK21" s="1"/>
       <c r="AL21" s="1"/>
